--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/6mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/6mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.64256641204</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>780.0193058656242</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>776.0002873078053</v>
+        <v>0.249968168</v>
+      </c>
+      <c r="Y2">
+        <v>0.262103512</v>
+      </c>
+      <c r="Z2">
+        <v>0.3621910214458807</v>
+      </c>
+      <c r="AA2">
+        <v>6.067671999999995</v>
+      </c>
+      <c r="AB2">
+        <v>0.06052376310437437</v>
+      </c>
+      <c r="AC2">
+        <v>47.20970368504958</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.64268215278</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>778.8233342970821</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>775.4952225304654</v>
+      </c>
+      <c r="X3">
+        <v>0.249978336</v>
+      </c>
+      <c r="Y3">
+        <v>0.262095872</v>
+      </c>
+      <c r="Z3">
+        <v>0.3621925103985024</v>
+      </c>
+      <c r="AA3">
+        <v>6.058768000000001</v>
+      </c>
+      <c r="AB3">
+        <v>0.06061052514197536</v>
+      </c>
+      <c r="AC3">
+        <v>47.20489128457037</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.64279847222</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>772.8114816876108</v>
       </c>
-      <c r="V4">
-        <v>3.862759142804546</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.250012016</v>
+      </c>
+      <c r="Y4">
+        <v>0.262082184</v>
+      </c>
+      <c r="Z4">
+        <v>0.362205852126376</v>
+      </c>
+      <c r="AA4">
+        <v>6.035083999999998</v>
+      </c>
+      <c r="AB4">
+        <v>0.06084410242955136</v>
+      </c>
+      <c r="AC4">
+        <v>47.02102095053435</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.64291421296</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>778.201592903162</v>
       </c>
-      <c r="V5">
-        <v>3.306111337985273</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>47.16279083042316</v>
+      </c>
+      <c r="X5">
+        <v>0.250025044</v>
+      </c>
+      <c r="Y5">
+        <v>0.262081548</v>
+      </c>
+      <c r="Z5">
+        <v>0.3622143846250149</v>
+      </c>
+      <c r="AA5">
+        <v>6.028252000000002</v>
+      </c>
+      <c r="AB5">
+        <v>0.0609125934486525</v>
+      </c>
+      <c r="AC5">
+        <v>47.40227724960408</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.64303053241</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>767.7324557859417</v>
       </c>
-      <c r="V6">
-        <v>5.23533881433016</v>
-      </c>
-      <c r="W6" t="b">
-        <v>0</v>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.250032352</v>
+      </c>
+      <c r="Y6">
+        <v>0.26207168</v>
+      </c>
+      <c r="Z6">
+        <v>0.3622122892789176</v>
+      </c>
+      <c r="AA6">
+        <v>6.019663999999999</v>
+      </c>
+      <c r="AB6">
+        <v>0.06099681097947807</v>
+      </c>
+      <c r="AC6">
+        <v>46.82923148838559</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.64314685185</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>772.7453490766038</v>
       </c>
-      <c r="V7">
-        <v>5.236132921307076</v>
-      </c>
-      <c r="W7" t="b">
-        <v>0</v>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.25002695</v>
+      </c>
+      <c r="Y7">
+        <v>0.262058948</v>
+      </c>
+      <c r="Z7">
+        <v>0.3621993483610499</v>
+      </c>
+      <c r="AA7">
+        <v>6.015999000000001</v>
+      </c>
+      <c r="AB7">
+        <v>0.06103085030591626</v>
+      </c>
+      <c r="AC7">
+        <v>47.16130572408721</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.6432625926</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>775.1026494331952</v>
       </c>
-      <c r="V8">
-        <v>3.763989871416656</v>
-      </c>
-      <c r="W8" t="b">
-        <v>0</v>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>0.250004072</v>
+      </c>
+      <c r="Y8">
+        <v>0.262050034</v>
+      </c>
+      <c r="Z8">
+        <v>0.3621771063112387</v>
+      </c>
+      <c r="AA8">
+        <v>6.022981000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.06095835936375235</v>
+      </c>
+      <c r="AC8">
+        <v>47.24898584794527</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.64337891203</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>770.2732838514336</v>
       </c>
-      <c r="V9">
-        <v>2.414910052534168</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.249971662</v>
+      </c>
+      <c r="Y9">
+        <v>0.262044624</v>
+      </c>
+      <c r="Z9">
+        <v>0.3621508204744863</v>
+      </c>
+      <c r="AA9">
+        <v>6.036481000000002</v>
+      </c>
+      <c r="AB9">
+        <v>0.0608214094458342</v>
+      </c>
+      <c r="AC9">
+        <v>46.84910678231531</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.64349523148</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>783.3300514639833</v>
       </c>
-      <c r="V10">
-        <v>6.601667675502481</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.249960224</v>
+      </c>
+      <c r="Y10">
+        <v>0.262040804</v>
+      </c>
+      <c r="Z10">
+        <v>0.3621401614611345</v>
+      </c>
+      <c r="AA10">
+        <v>6.040289999999999</v>
+      </c>
+      <c r="AB10">
+        <v>0.06078235204935667</v>
+      </c>
+      <c r="AC10">
+        <v>47.61264295892451</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.64361155093</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>765.5460183554115</v>
       </c>
-      <c r="V11">
-        <v>9.211388360473331</v>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.24996086</v>
+      </c>
+      <c r="Y11">
+        <v>0.26203189</v>
+      </c>
+      <c r="Z11">
+        <v>0.3621341504317312</v>
+      </c>
+      <c r="AA11">
+        <v>6.035515000000004</v>
+      </c>
+      <c r="AB11">
+        <v>0.06082815652633234</v>
+      </c>
+      <c r="AC11">
+        <v>46.56675303263346</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.64372729167</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>784.4568760782555</v>
       </c>
-      <c r="V12">
-        <v>10.60787527525153</v>
-      </c>
-      <c r="W12" t="b">
-        <v>0</v>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.249953234</v>
+      </c>
+      <c r="Y12">
+        <v>0.262019794</v>
+      </c>
+      <c r="Z12">
+        <v>0.3621201342577642</v>
+      </c>
+      <c r="AA12">
+        <v>6.033280000000005</v>
+      </c>
+      <c r="AB12">
+        <v>0.06084778957886421</v>
+      </c>
+      <c r="AC12">
+        <v>47.73246692930285</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.64384361111</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>766.3970027867762</v>
       </c>
-      <c r="V13">
-        <v>10.6810091409969</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.249909386</v>
+      </c>
+      <c r="Y13">
+        <v>0.262011836</v>
+      </c>
+      <c r="Z13">
+        <v>0.3620841109673109</v>
+      </c>
+      <c r="AA13">
+        <v>6.051225000000002</v>
+      </c>
+      <c r="AB13">
+        <v>0.06066635361068039</v>
+      </c>
+      <c r="AC13">
+        <v>46.49451157722817</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.64395993055</v>
       </c>
@@ -1411,11 +1642,26 @@
       <c r="U14">
         <v>785.9984913109712</v>
       </c>
-      <c r="V14">
-        <v>10.89918921444913</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.249933852</v>
+      </c>
+      <c r="Y14">
+        <v>0.262010882</v>
+      </c>
+      <c r="Z14">
+        <v>0.3621003074591015</v>
+      </c>
+      <c r="AA14">
+        <v>6.038514999999997</v>
+      </c>
+      <c r="AB14">
+        <v>0.0607932251946464</v>
+      </c>
+      <c r="AC14">
+        <v>47.7833832849202</v>
       </c>
     </row>
   </sheetData>
